--- a/docs/tgr/evidence/harmony-compat-v1/natal-harmony-compat-v1.xlsx
+++ b/docs/tgr/evidence/harmony-compat-v1/natal-harmony-compat-v1.xlsx
@@ -192,7 +192,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -212,12 +212,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_REVIEW_ASSERTION:PR#1@bd7848b3f6f8c7bbbf6142c68f4fb0cdf09f233e</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -242,7 +242,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -267,7 +267,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -283,16 +283,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>117203</v>
+        <v>195339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_REVIEW_ASSERTION:PR#1@bd7848b3f6f8c7bbbf6142c68f4fb0cdf09f233e</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -312,12 +312,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -337,12 +337,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_REVIEW_ASSERTION:PR#1@bd7848b3f6f8c7bbbf6142c68f4fb0cdf09f233e</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -364,12 +364,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -391,12 +391,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -418,12 +418,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -445,12 +445,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -472,12 +472,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -499,12 +499,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT:missing COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json:not_applicable_to_harmony_compat_v1</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERIVED_FROM_REVIEW_RULES:HARMONY_COMPAT_V1 compatibility placeholder</t>
+          <t xml:space="preserve">DERIVED_FROM_CANONICAL_HARMONY_RULES:COTAS_NATAL_HARMONY_GOLDEN_V1</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">current_document</t>
+          <t xml:space="preserve">historical_primary</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_REVIEW_ASSERTION:PR#1@bd7848b3f6f8c7bbbf6142c68f4fb0cdf09f233e</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1:docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paridade com o workbook ausente não certificada</t>
+          <t xml:space="preserve">Golden Harmony canônico certificado</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE_CONFLICT</t>
+          <t xml:space="preserve">CANONICAL_FROM_HARMONY_MASTER_V1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PR #1 review on bd7848b and user execution prompt</t>
+          <t xml:space="preserve">docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">missingSource</t>
+          <t xml:space="preserve">SC-001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">missing_source</t>
+          <t xml:space="preserve">source_conflict</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTAS_NATAL_ESTUDO_VIABILIDADE_HARMONY_MASTER_V1</t>
+          <t xml:space="preserve">Preservar 4.457 no cronograma mensal (44×100 + 57) e registrar 4.458 somente na linha indicadora publicada.</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PR #1 review on bd7848b and user execution prompt</t>
+          <t xml:space="preserve">docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PR #1 review on bd7848b and user execution prompt</t>
+          <t xml:space="preserve">docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PR #1 review on bd7848b and user execution prompt</t>
+          <t xml:space="preserve">docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PR #1 review on bd7848b and user execution prompt</t>
+          <t xml:space="preserve">docs/tgr/golden/COTAS_NATAL_HARMONY_GOLDEN_V1_RULES.json</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z121"/>
+  <dimension ref="A1:Z145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,13 +1536,13 @@
         <v>33600.00000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>48629.28000000</v>
+        <v>35700.00000000</v>
       </c>
       <c r="R2" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S2" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T2" t="n">
         <v>0.00000000</v>
@@ -1557,13 +1557,13 @@
         <v>985500.00000000</v>
       </c>
       <c r="X2" t="n">
-        <v>-1178842.28000000</v>
+        <v>-1165913.40000000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1178842.28000000</v>
+        <v>-1165913.40000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1161420.96551724</v>
+        <v>-177942.06403756</v>
       </c>
     </row>
     <row r="3">
@@ -1616,13 +1616,13 @@
         <v>67200.00000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>48629.28000000</v>
+        <v>35700.00000000</v>
       </c>
       <c r="R3" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S3" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T3" t="n">
         <v>0.00000000</v>
@@ -1637,13 +1637,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X3" t="n">
-        <v>-177844.28000000</v>
+        <v>-164915.40000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1356686.56000000</v>
+        <v>-1330828.80000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-172626.63981169</v>
+        <v>-160428.26175502</v>
       </c>
     </row>
     <row r="4">
@@ -1696,13 +1696,13 @@
         <v>100800.00000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>48629.28000000</v>
+        <v>35700.00000000</v>
       </c>
       <c r="R4" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S4" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T4" t="n">
         <v>0.00000000</v>
@@ -1717,13 +1717,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X4" t="n">
-        <v>-162346.28000000</v>
+        <v>-149417.40000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1519032.84000000</v>
+        <v>-1480246.20000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-155254.50643464</v>
+        <v>-143360.88495463</v>
       </c>
     </row>
     <row r="5">
@@ -1776,13 +1776,13 @@
         <v>134400.00000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>48629.28000000</v>
+        <v>35700.00000000</v>
       </c>
       <c r="R5" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S5" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T5" t="n">
         <v>0.00000000</v>
@@ -1797,13 +1797,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X5" t="n">
-        <v>-146848.28000000</v>
+        <v>-133919.40000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1665881.12000000</v>
+        <v>-1614165.60000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-138358.13366073</v>
+        <v>-126730.98949369</v>
       </c>
     </row>
     <row r="6">
@@ -1856,13 +1856,13 @@
         <v>192800.00000000</v>
       </c>
       <c r="Q6" t="n">
-        <v>48629.28000000</v>
+        <v>35853.91600000</v>
       </c>
       <c r="R6" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S6" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T6" t="n">
         <v>0.00000000</v>
@@ -1877,13 +1877,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X6" t="n">
-        <v>-108286.28000000</v>
+        <v>-95511.31600000</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1774167.40000000</v>
+        <v>-1709676.91600000</v>
       </c>
       <c r="Z6" t="n">
-        <v>-100517.85750977</v>
+        <v>-89146.43754258</v>
       </c>
     </row>
     <row r="7">
@@ -1936,13 +1936,13 @@
         <v>251200.00000000</v>
       </c>
       <c r="Q7" t="n">
-        <v>48629.28000000</v>
+        <v>36007.83200000</v>
       </c>
       <c r="R7" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S7" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T7" t="n">
         <v>0.00000000</v>
@@ -1957,13 +1957,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X7" t="n">
-        <v>-69724.28000000</v>
+        <v>-57103.23200000</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1843891.68000000</v>
+        <v>-1766780.14800000</v>
       </c>
       <c r="Z7" t="n">
-        <v>-63765.79590293</v>
+        <v>-52567.78597916</v>
       </c>
     </row>
     <row r="8">
@@ -2016,13 +2016,13 @@
         <v>309600.00000000</v>
       </c>
       <c r="Q8" t="n">
-        <v>48629.28000000</v>
+        <v>36161.74800000</v>
       </c>
       <c r="R8" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S8" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T8" t="n">
         <v>0.00000000</v>
@@ -2037,13 +2037,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X8" t="n">
-        <v>-31162.28000000</v>
+        <v>-18695.14800000</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1875053.96000000</v>
+        <v>-1785475.29600000</v>
       </c>
       <c r="Z8" t="n">
-        <v>-28078.04913799</v>
+        <v>-16974.52916071</v>
       </c>
     </row>
     <row r="9">
@@ -2096,13 +2096,13 @@
         <v>368000.00000000</v>
       </c>
       <c r="Q9" t="n">
-        <v>48629.28000000</v>
+        <v>36315.66400000</v>
       </c>
       <c r="R9" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S9" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T9" t="n">
         <v>0.00000000</v>
@@ -2117,13 +2117,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X9" t="n">
-        <v>7399.72000000</v>
+        <v>19712.93600000</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1867654.24000000</v>
+        <v>-1765762.36000000</v>
       </c>
       <c r="Z9" t="n">
-        <v>6568.81375701</v>
+        <v>17653.46552277</v>
       </c>
     </row>
     <row r="10">
@@ -2176,13 +2176,13 @@
         <v>392800.00000000</v>
       </c>
       <c r="Q10" t="n">
-        <v>48629.28000000</v>
+        <v>36469.58000000</v>
       </c>
       <c r="R10" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S10" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T10" t="n">
         <v>0.00000000</v>
@@ -2197,13 +2197,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X10" t="n">
-        <v>30463.72000000</v>
+        <v>42623.02000000</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1837190.52000000</v>
+        <v>-1723139.34000000</v>
       </c>
       <c r="Z10" t="n">
-        <v>26643.33311957</v>
+        <v>37647.20270168</v>
       </c>
     </row>
     <row r="11">
@@ -2256,13 +2256,13 @@
         <v>417600.00000000</v>
       </c>
       <c r="Q11" t="n">
-        <v>48629.28000000</v>
+        <v>36623.49600000</v>
       </c>
       <c r="R11" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S11" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T11" t="n">
         <v>0.00000000</v>
@@ -2277,13 +2277,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X11" t="n">
-        <v>53527.72000000</v>
+        <v>65533.10400000</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1783662.80000000</v>
+        <v>-1657606.23600000</v>
       </c>
       <c r="Z11" t="n">
-        <v>46123.08231280</v>
+        <v>57089.87159560</v>
       </c>
     </row>
     <row r="12">
@@ -2336,13 +2336,13 @@
         <v>442400.00000000</v>
       </c>
       <c r="Q12" t="n">
-        <v>48629.28000000</v>
+        <v>36777.41200000</v>
       </c>
       <c r="R12" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S12" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T12" t="n">
         <v>0.00000000</v>
@@ -2357,13 +2357,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X12" t="n">
-        <v>76591.72000000</v>
+        <v>88443.18800000</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1707071.08000000</v>
+        <v>-1569163.04800000</v>
       </c>
       <c r="Z12" t="n">
-        <v>65021.25649777</v>
+        <v>75992.81784435</v>
       </c>
     </row>
     <row r="13">
@@ -2416,13 +2416,13 @@
         <v>467200.00000000</v>
       </c>
       <c r="Q13" t="n">
-        <v>48629.28000000</v>
+        <v>36931.32800000</v>
       </c>
       <c r="R13" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S13" t="n">
-        <v>117203.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T13" t="n">
         <v>0.00000000</v>
@@ -2437,13 +2437,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X13" t="n">
-        <v>99655.72000000</v>
+        <v>111353.27200000</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1607415.36000000</v>
+        <v>-1457809.77600000</v>
       </c>
       <c r="Z13" t="n">
-        <v>83350.79072793</v>
+        <v>94367.17966102</v>
       </c>
     </row>
     <row r="14">
@@ -2496,7 +2496,7 @@
         <v>492000.00000000</v>
       </c>
       <c r="Q14" t="n">
-        <v>48629.28000000</v>
+        <v>37085.24400000</v>
       </c>
       <c r="R14" t="n">
         <v>0.00000000</v>
@@ -2517,13 +2517,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X14" t="n">
-        <v>44583.72000000</v>
+        <v>56127.75600000</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1562831.64000000</v>
+        <v>-1401682.02000000</v>
       </c>
       <c r="Z14" t="n">
-        <v>36738.18978257</v>
+        <v>46914.32853111</v>
       </c>
     </row>
     <row r="15">
@@ -2576,7 +2576,7 @@
         <v>516800.00000000</v>
       </c>
       <c r="Q15" t="n">
-        <v>48629.28000000</v>
+        <v>37239.16000000</v>
       </c>
       <c r="R15" t="n">
         <v>0.00000000</v>
@@ -2597,13 +2597,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X15" t="n">
-        <v>67647.72000000</v>
+        <v>79037.84000000</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1495183.92000000</v>
+        <v>-1322644.18000000</v>
       </c>
       <c r="Z15" t="n">
-        <v>54919.75260540</v>
+        <v>65158.74654043</v>
       </c>
     </row>
     <row r="16">
@@ -2656,7 +2656,7 @@
         <v>541600.00000000</v>
       </c>
       <c r="Q16" t="n">
-        <v>48629.28000000</v>
+        <v>37393.07600000</v>
       </c>
       <c r="R16" t="n">
         <v>0.00000000</v>
@@ -2677,13 +2677,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X16" t="n">
-        <v>90711.72000000</v>
+        <v>101947.92400000</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1404472.20000000</v>
+        <v>-1220696.25600000</v>
       </c>
       <c r="Z16" t="n">
-        <v>72555.90575496</v>
+        <v>82894.53074117</v>
       </c>
     </row>
     <row r="17">
@@ -2736,7 +2736,7 @@
         <v>566400.00000000</v>
       </c>
       <c r="Q17" t="n">
-        <v>48629.28000000</v>
+        <v>37546.99200000</v>
       </c>
       <c r="R17" t="n">
         <v>0.00000000</v>
@@ -2757,13 +2757,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X17" t="n">
-        <v>113775.72000000</v>
+        <v>124858.00800000</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1290696.48000000</v>
+        <v>-1095838.24800000</v>
       </c>
       <c r="Z17" t="n">
-        <v>89658.79888098</v>
+        <v>100132.19246530</v>
       </c>
     </row>
     <row r="18">
@@ -2816,7 +2816,7 @@
         <v>591200.00000000</v>
       </c>
       <c r="Q18" t="n">
-        <v>48629.28000000</v>
+        <v>37700.90800000</v>
       </c>
       <c r="R18" t="n">
         <v>0.00000000</v>
@@ -2837,13 +2837,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X18" t="n">
-        <v>136839.72000000</v>
+        <v>147768.09200000</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1153856.76000000</v>
+        <v>-948070.15600000</v>
       </c>
       <c r="Z18" t="n">
-        <v>106240.34164715</v>
+        <v>116882.05051264</v>
       </c>
     </row>
     <row r="19">
@@ -2896,7 +2896,7 @@
         <v>616000.00000000</v>
       </c>
       <c r="Q19" t="n">
-        <v>48629.28000000</v>
+        <v>37854.82400000</v>
       </c>
       <c r="R19" t="n">
         <v>0.00000000</v>
@@ -2917,13 +2917,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X19" t="n">
-        <v>159903.72000000</v>
+        <v>170678.17600000</v>
       </c>
       <c r="Y19" t="n">
-        <v>-993953.04000000</v>
+        <v>-777391.98000000</v>
       </c>
       <c r="Z19" t="n">
-        <v>122312.20817077</v>
+        <v>133154.23445321</v>
       </c>
     </row>
     <row r="20">
@@ -2976,7 +2976,7 @@
         <v>640800.00000000</v>
       </c>
       <c r="Q20" t="n">
-        <v>48629.28000000</v>
+        <v>38008.74000000</v>
       </c>
       <c r="R20" t="n">
         <v>0.00000000</v>
@@ -2997,13 +2997,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X20" t="n">
-        <v>182967.72000000</v>
+        <v>193588.26000000</v>
       </c>
       <c r="Y20" t="n">
-        <v>-810985.32000000</v>
+        <v>-583803.72000000</v>
       </c>
       <c r="Z20" t="n">
-        <v>137885.84138370</v>
+        <v>148958.68787518</v>
       </c>
     </row>
     <row r="21">
@@ -3056,7 +3056,7 @@
         <v>665600.00000000</v>
       </c>
       <c r="Q21" t="n">
-        <v>48629.28000000</v>
+        <v>38162.65600000</v>
       </c>
       <c r="R21" t="n">
         <v>0.00000000</v>
@@ -3077,13 +3077,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X21" t="n">
-        <v>206031.72000000</v>
+        <v>216498.34400000</v>
       </c>
       <c r="Y21" t="n">
-        <v>-604953.60000000</v>
+        <v>-367305.37600000</v>
       </c>
       <c r="Z21" t="n">
-        <v>152972.45731576</v>
+        <v>164305.17157943</v>
       </c>
     </row>
     <row r="22">
@@ -3136,7 +3136,7 @@
         <v>690400.00000000</v>
       </c>
       <c r="Q22" t="n">
-        <v>48629.28000000</v>
+        <v>38316.57200000</v>
       </c>
       <c r="R22" t="n">
         <v>0.00000000</v>
@@ -3157,13 +3157,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X22" t="n">
-        <v>229095.72000000</v>
+        <v>239408.42800000</v>
       </c>
       <c r="Y22" t="n">
-        <v>-375857.88000000</v>
+        <v>-127896.94800000</v>
       </c>
       <c r="Z22" t="n">
-        <v>167583.04930214</v>
+        <v>179203.26672141</v>
       </c>
     </row>
     <row r="23">
@@ -3216,7 +3216,7 @@
         <v>715200.00000000</v>
       </c>
       <c r="Q23" t="n">
-        <v>48629.28000000</v>
+        <v>38470.48800000</v>
       </c>
       <c r="R23" t="n">
         <v>0.00000000</v>
@@ -3237,13 +3237,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X23" t="n">
-        <v>252159.72000000</v>
+        <v>262318.51200000</v>
       </c>
       <c r="Y23" t="n">
-        <v>-123698.16000000</v>
+        <v>134421.56400000</v>
       </c>
       <c r="Z23" t="n">
-        <v>181728.39211589</v>
+        <v>193662.37790123</v>
       </c>
     </row>
     <row r="24">
@@ -3296,7 +3296,7 @@
         <v>740000.00000000</v>
       </c>
       <c r="Q24" t="n">
-        <v>48629.28000000</v>
+        <v>38624.40400000</v>
       </c>
       <c r="R24" t="n">
         <v>0.00000000</v>
@@ -3317,13 +3317,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X24" t="n">
-        <v>275223.72000000</v>
+        <v>285228.59600000</v>
       </c>
       <c r="Y24" t="n">
-        <v>151525.56000000</v>
+        <v>419650.16000000</v>
       </c>
       <c r="Z24" t="n">
-        <v>195419.04602694</v>
+        <v>207691.73620290</v>
       </c>
     </row>
     <row r="25">
@@ -3376,7 +3376,7 @@
         <v>764800.00000000</v>
       </c>
       <c r="Q25" t="n">
-        <v>48629.28000000</v>
+        <v>38778.32000000</v>
       </c>
       <c r="R25" t="n">
         <v>0.00000000</v>
@@ -3397,13 +3397,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X25" t="n">
-        <v>298287.72000000</v>
+        <v>308138.68000000</v>
       </c>
       <c r="Y25" t="n">
-        <v>449813.28000000</v>
+        <v>727788.84000000</v>
       </c>
       <c r="Z25" t="n">
-        <v>208665.36078896</v>
+        <v>221300.40218328</v>
       </c>
     </row>
     <row r="26">
@@ -3456,7 +3456,7 @@
         <v>789600.00000000</v>
       </c>
       <c r="Q26" t="n">
-        <v>48629.28000000</v>
+        <v>38932.23600000</v>
       </c>
       <c r="R26" t="n">
         <v>0.00000000</v>
@@ -3477,13 +3477,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X26" t="n">
-        <v>321351.72000000</v>
+        <v>331048.76400000</v>
       </c>
       <c r="Y26" t="n">
-        <v>771165.00000000</v>
+        <v>1058837.60400000</v>
       </c>
       <c r="Z26" t="n">
-        <v>221477.47955509</v>
+        <v>234497.26881182</v>
       </c>
     </row>
     <row r="27">
@@ -3536,7 +3536,7 @@
         <v>814400.00000000</v>
       </c>
       <c r="Q27" t="n">
-        <v>48629.28000000</v>
+        <v>39086.15200000</v>
       </c>
       <c r="R27" t="n">
         <v>0.00000000</v>
@@ -3557,13 +3557,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X27" t="n">
-        <v>344415.72000000</v>
+        <v>353958.84800000</v>
       </c>
       <c r="Y27" t="n">
-        <v>1115580.72000000</v>
+        <v>1412796.45200000</v>
       </c>
       <c r="Z27" t="n">
-        <v>233865.34272404</v>
+        <v>247291.06436173</v>
       </c>
     </row>
     <row r="28">
@@ -3616,7 +3616,7 @@
         <v>839200.00000000</v>
       </c>
       <c r="Q28" t="n">
-        <v>48629.28000000</v>
+        <v>39240.06800000</v>
       </c>
       <c r="R28" t="n">
         <v>0.00000000</v>
@@ -3637,13 +3637,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X28" t="n">
-        <v>367479.72000000</v>
+        <v>376868.93200000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1483060.44000000</v>
+        <v>1789665.38400000</v>
       </c>
       <c r="Z28" t="n">
-        <v>245838.69171755</v>
+        <v>259690.35525336</v>
       </c>
     </row>
     <row r="29">
@@ -3696,7 +3696,7 @@
         <v>864000.00000000</v>
       </c>
       <c r="Q29" t="n">
-        <v>48629.28000000</v>
+        <v>39393.98400000</v>
       </c>
       <c r="R29" t="n">
         <v>0.00000000</v>
@@ -3717,13 +3717,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X29" t="n">
-        <v>390543.72000000</v>
+        <v>399779.01600000</v>
       </c>
       <c r="Y29" t="n">
-        <v>1873604.16000000</v>
+        <v>2189444.40000000</v>
       </c>
       <c r="Z29" t="n">
-        <v>257407.07269052</v>
+        <v>271703.54885059</v>
       </c>
     </row>
     <row r="30">
@@ -3776,7 +3776,7 @@
         <v>888800.00000000</v>
       </c>
       <c r="Q30" t="n">
-        <v>48629.28000000</v>
+        <v>39547.90000000</v>
       </c>
       <c r="R30" t="n">
         <v>0.00000000</v>
@@ -3797,13 +3797,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X30" t="n">
-        <v>413607.72000000</v>
+        <v>422689.10000000</v>
       </c>
       <c r="Y30" t="n">
-        <v>2287211.88000000</v>
+        <v>2612133.50000000</v>
       </c>
       <c r="Z30" t="n">
-        <v>268579.84017491</v>
+        <v>283338.89621105</v>
       </c>
     </row>
     <row r="31">
@@ -3856,7 +3856,7 @@
         <v>913600.00000000</v>
       </c>
       <c r="Q31" t="n">
-        <v>48629.28000000</v>
+        <v>39701.81600000</v>
       </c>
       <c r="R31" t="n">
         <v>0.00000000</v>
@@ -3877,13 +3877,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X31" t="n">
-        <v>436671.72000000</v>
+        <v>445599.18400000</v>
       </c>
       <c r="Y31" t="n">
-        <v>2723883.60000000</v>
+        <v>3057732.68400000</v>
       </c>
       <c r="Z31" t="n">
-        <v>279366.16065865</v>
+        <v>294604.49479072</v>
       </c>
     </row>
     <row r="32">
@@ -3936,7 +3936,7 @@
         <v>938400.00000000</v>
       </c>
       <c r="Q32" t="n">
-        <v>48629.28000000</v>
+        <v>39855.73200000</v>
       </c>
       <c r="R32" t="n">
         <v>0.00000000</v>
@@ -3957,13 +3957,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X32" t="n">
-        <v>459735.72000000</v>
+        <v>468509.26800000</v>
       </c>
       <c r="Y32" t="n">
-        <v>3183619.32000000</v>
+        <v>3526241.95200000</v>
       </c>
       <c r="Z32" t="n">
-        <v>289775.01610050</v>
+        <v>305508.29110388</v>
       </c>
     </row>
     <row r="33">
@@ -4016,7 +4016,7 @@
         <v>963200.00000000</v>
       </c>
       <c r="Q33" t="n">
-        <v>48629.28000000</v>
+        <v>40009.64800000</v>
       </c>
       <c r="R33" t="n">
         <v>0.00000000</v>
@@ -4037,13 +4037,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X33" t="n">
-        <v>482799.72000000</v>
+        <v>491419.35200000</v>
       </c>
       <c r="Y33" t="n">
-        <v>3666419.04000000</v>
+        <v>4017661.30400000</v>
       </c>
       <c r="Z33" t="n">
-        <v>299815.20738224</v>
+        <v>316058.08333892</v>
       </c>
     </row>
     <row r="34">
@@ -4096,7 +4096,7 @@
         <v>988000.00000000</v>
       </c>
       <c r="Q34" t="n">
-        <v>48629.28000000</v>
+        <v>40163.56400000</v>
       </c>
       <c r="R34" t="n">
         <v>0.00000000</v>
@@ -4117,13 +4117,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X34" t="n">
-        <v>505863.72000000</v>
+        <v>514329.43600000</v>
       </c>
       <c r="Y34" t="n">
-        <v>4172282.76000000</v>
+        <v>4531990.74000000</v>
       </c>
       <c r="Z34" t="n">
-        <v>309495.35769900</v>
+        <v>326261.52393085</v>
       </c>
     </row>
     <row r="35">
@@ -4176,7 +4176,7 @@
         <v>1012800.00000000</v>
       </c>
       <c r="Q35" t="n">
-        <v>48629.28000000</v>
+        <v>40317.48000000</v>
       </c>
       <c r="R35" t="n">
         <v>0.00000000</v>
@@ -4197,13 +4197,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X35" t="n">
-        <v>528927.72000000</v>
+        <v>537239.52000000</v>
       </c>
       <c r="Y35" t="n">
-        <v>4701210.48000000</v>
+        <v>5069230.26000000</v>
       </c>
       <c r="Z35" t="n">
-        <v>318823.91588898</v>
+        <v>336126.12209117</v>
       </c>
     </row>
     <row r="36">
@@ -4256,7 +4256,7 @@
         <v>1037600.00000000</v>
       </c>
       <c r="Q36" t="n">
-        <v>48629.28000000</v>
+        <v>40471.39600000</v>
       </c>
       <c r="R36" t="n">
         <v>0.00000000</v>
@@ -4277,13 +4277,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X36" t="n">
-        <v>551991.72000000</v>
+        <v>560149.60400000</v>
       </c>
       <c r="Y36" t="n">
-        <v>5253202.20000000</v>
+        <v>5629379.86400000</v>
       </c>
       <c r="Z36" t="n">
-        <v>327809.15970360</v>
+        <v>345659.24629578</v>
       </c>
     </row>
     <row r="37">
@@ -4336,7 +4336,7 @@
         <v>1062400.00000000</v>
       </c>
       <c r="Q37" t="n">
-        <v>48629.28000000</v>
+        <v>40625.31200000</v>
       </c>
       <c r="R37" t="n">
         <v>0.00000000</v>
@@ -4357,13 +4357,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X37" t="n">
-        <v>575055.72000000</v>
+        <v>583059.68800000</v>
       </c>
       <c r="Y37" t="n">
-        <v>5828257.92000000</v>
+        <v>6212439.55200000</v>
       </c>
       <c r="Z37" t="n">
-        <v>336459.19901897</v>
+        <v>354868.12673155</v>
       </c>
     </row>
     <row r="38">
@@ -4416,7 +4416,7 @@
         <v>1087200.00000000</v>
       </c>
       <c r="Q38" t="n">
-        <v>48629.28000000</v>
+        <v>40779.22800000</v>
       </c>
       <c r="R38" t="n">
         <v>0.00000000</v>
@@ -4437,13 +4437,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X38" t="n">
-        <v>598119.72000000</v>
+        <v>605969.77200000</v>
       </c>
       <c r="Y38" t="n">
-        <v>6426377.64000000</v>
+        <v>6818409.32400000</v>
       </c>
       <c r="Z38" t="n">
-        <v>344781.97898994</v>
+        <v>363759.85770238</v>
       </c>
     </row>
     <row r="39">
@@ -4454,10 +4454,10 @@
         <v>600.00000000</v>
       </c>
       <c r="C39" t="n">
-        <v>18.00000000</v>
+        <v>17.00000000</v>
       </c>
       <c r="D39" t="n">
-        <v>504000.00000000</v>
+        <v>476000.00000000</v>
       </c>
       <c r="E39" t="n">
         <v>38400.00000000</v>
@@ -4475,7 +4475,7 @@
         <v>843200.00000000</v>
       </c>
       <c r="J39" t="n">
-        <v>168000.00000000</v>
+        <v>140000.00000000</v>
       </c>
       <c r="K39" t="n">
         <v>270800.00000000</v>
@@ -4496,7 +4496,7 @@
         <v>1083200.00000000</v>
       </c>
       <c r="Q39" t="n">
-        <v>6947.04000000</v>
+        <v>10333.14400000</v>
       </c>
       <c r="R39" t="n">
         <v>0.00000000</v>
@@ -4517,13 +4517,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X39" t="n">
-        <v>686445.96000000</v>
+        <v>683059.85600000</v>
       </c>
       <c r="Y39" t="n">
-        <v>7112823.60000000</v>
+        <v>7501469.18000000</v>
       </c>
       <c r="Z39" t="n">
-        <v>389849.29026156</v>
+        <v>404419.79598649</v>
       </c>
     </row>
     <row r="40">
@@ -4576,7 +4576,7 @@
         <v>1074400.00000000</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.00000000</v>
+        <v>5387.06000000</v>
       </c>
       <c r="R40" t="n">
         <v>0.00000000</v>
@@ -4597,13 +4597,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X40" t="n">
-        <v>707103.00000000</v>
+        <v>701715.94000000</v>
       </c>
       <c r="Y40" t="n">
-        <v>7819926.60000000</v>
+        <v>8203185.12000000</v>
       </c>
       <c r="Z40" t="n">
-        <v>395646.23025332</v>
+        <v>409774.39543202</v>
       </c>
     </row>
     <row r="41">
@@ -4656,7 +4656,7 @@
         <v>1065600.00000000</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.00000000</v>
+        <v>5540.97600000</v>
       </c>
       <c r="R41" t="n">
         <v>0.00000000</v>
@@ -4677,13 +4677,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X41" t="n">
-        <v>714669.00000000</v>
+        <v>709128.02400000</v>
       </c>
       <c r="Y41" t="n">
-        <v>8534595.60000000</v>
+        <v>8912313.14400000</v>
       </c>
       <c r="Z41" t="n">
-        <v>393970.09235667</v>
+        <v>408430.30392733</v>
       </c>
     </row>
     <row r="42">
@@ -4736,7 +4736,7 @@
         <v>1056800.00000000</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.00000000</v>
+        <v>5694.89200000</v>
       </c>
       <c r="R42" t="n">
         <v>0.00000000</v>
@@ -4757,13 +4757,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X42" t="n">
-        <v>722235.00000000</v>
+        <v>716540.10800000</v>
       </c>
       <c r="Y42" t="n">
-        <v>9256830.60000000</v>
+        <v>9628853.25200000</v>
       </c>
       <c r="Z42" t="n">
-        <v>392257.08678270</v>
+        <v>407046.14547960</v>
       </c>
     </row>
     <row r="43">
@@ -4816,7 +4816,7 @@
         <v>1026742.85714286</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R43" t="n">
         <v>0.00000000</v>
@@ -4837,13 +4837,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X43" t="n">
-        <v>710031.85714286</v>
+        <v>704314.97714286</v>
       </c>
       <c r="Y43" t="n">
-        <v>9966862.45714286</v>
+        <v>10333168.22914286</v>
       </c>
       <c r="Z43" t="n">
-        <v>379930.41347092</v>
+        <v>394620.73225802</v>
       </c>
     </row>
     <row r="44">
@@ -4896,7 +4896,7 @@
         <v>993142.85714286</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R44" t="n">
         <v>0.00000000</v>
@@ -4917,13 +4917,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X44" t="n">
-        <v>694533.85714286</v>
+        <v>688816.97714286</v>
       </c>
       <c r="Y44" t="n">
-        <v>10661396.31428571</v>
+        <v>11021985.20628571</v>
       </c>
       <c r="Z44" t="n">
-        <v>366145.41899912</v>
+        <v>380650.71483582</v>
       </c>
     </row>
     <row r="45">
@@ -4976,7 +4976,7 @@
         <v>959542.85714286</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R45" t="n">
         <v>0.00000000</v>
@@ -4997,13 +4997,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X45" t="n">
-        <v>679035.85714286</v>
+        <v>673318.97714286</v>
       </c>
       <c r="Y45" t="n">
-        <v>11340432.17142857</v>
+        <v>11695304.18342857</v>
       </c>
       <c r="Z45" t="n">
-        <v>352684.88640568</v>
+        <v>366989.37842229</v>
       </c>
     </row>
     <row r="46">
@@ -5056,7 +5056,7 @@
         <v>925942.85714286</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R46" t="n">
         <v>0.00000000</v>
@@ -5077,13 +5077,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X46" t="n">
-        <v>663537.85714286</v>
+        <v>657820.97714286</v>
       </c>
       <c r="Y46" t="n">
-        <v>12003970.02857143</v>
+        <v>12353125.16057143</v>
       </c>
       <c r="Z46" t="n">
-        <v>339542.23631189</v>
+        <v>353630.88761640</v>
       </c>
     </row>
     <row r="47">
@@ -5136,7 +5136,7 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R47" t="n">
         <v>0.00000000</v>
@@ -5157,13 +5157,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X47" t="n">
-        <v>661323.85714286</v>
+        <v>655606.97714286</v>
       </c>
       <c r="Y47" t="n">
-        <v>12665293.88571429</v>
+        <v>13008732.13771429</v>
       </c>
       <c r="Z47" t="n">
-        <v>333408.17677787</v>
+        <v>347612.88981550</v>
       </c>
     </row>
     <row r="48">
@@ -5216,7 +5216,7 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R48" t="n">
         <v>0.00000000</v>
@@ -5237,13 +5237,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X48" t="n">
-        <v>661323.85714286</v>
+        <v>655606.97714286</v>
       </c>
       <c r="Y48" t="n">
-        <v>13326617.74285714</v>
+        <v>13664339.11485714</v>
       </c>
       <c r="Z48" t="n">
-        <v>328480.96234273</v>
+        <v>342851.22446465</v>
       </c>
     </row>
     <row r="49">
@@ -5296,7 +5296,7 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R49" t="n">
         <v>0.00000000</v>
@@ -5317,13 +5317,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X49" t="n">
-        <v>661323.85714286</v>
+        <v>655606.97714286</v>
       </c>
       <c r="Y49" t="n">
-        <v>13987941.60000000</v>
+        <v>14319946.09200000</v>
       </c>
       <c r="Z49" t="n">
-        <v>323626.56388446</v>
+        <v>338154.78528228</v>
       </c>
     </row>
     <row r="50">
@@ -5376,13 +5376,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R50" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S50" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T50" t="n">
         <v>0.00000000</v>
@@ -5397,13 +5397,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X50" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y50" t="n">
-        <v>14844604.45714286</v>
+        <v>15014620.86914286</v>
       </c>
       <c r="Z50" t="n">
-        <v>413022.64836042</v>
+        <v>353397.38690559</v>
       </c>
     </row>
     <row r="51">
@@ -5456,13 +5456,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R51" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S51" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T51" t="n">
         <v>0.00000000</v>
@@ -5477,13 +5477,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X51" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y51" t="n">
-        <v>15701267.31428571</v>
+        <v>15709295.64628571</v>
       </c>
       <c r="Z51" t="n">
-        <v>406918.86537972</v>
+        <v>348556.48444884</v>
       </c>
     </row>
     <row r="52">
@@ -5536,13 +5536,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R52" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S52" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T52" t="n">
         <v>0.00000000</v>
@@ -5557,13 +5557,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X52" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y52" t="n">
-        <v>16557930.17142857</v>
+        <v>16403970.42342857</v>
       </c>
       <c r="Z52" t="n">
-        <v>400905.28608840</v>
+        <v>343781.89356501</v>
       </c>
     </row>
     <row r="53">
@@ -5616,13 +5616,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R53" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S53" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T53" t="n">
         <v>0.00000000</v>
@@ -5637,13 +5637,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X53" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y53" t="n">
-        <v>17414593.02857143</v>
+        <v>17098645.20057143</v>
       </c>
       <c r="Z53" t="n">
-        <v>394980.57742699</v>
+        <v>339072.70590599</v>
       </c>
     </row>
     <row r="54">
@@ -5696,13 +5696,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R54" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S54" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T54" t="n">
         <v>0.00000000</v>
@@ -5717,13 +5717,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X54" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y54" t="n">
-        <v>18271255.88571429</v>
+        <v>17793319.97771429</v>
       </c>
       <c r="Z54" t="n">
-        <v>389143.42603645</v>
+        <v>334428.02556636</v>
       </c>
     </row>
     <row r="55">
@@ -5776,13 +5776,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R55" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S55" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T55" t="n">
         <v>0.00000000</v>
@@ -5797,13 +5797,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X55" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y55" t="n">
-        <v>19127918.74285714</v>
+        <v>18487994.75485714</v>
       </c>
       <c r="Z55" t="n">
-        <v>383392.53796694</v>
+        <v>329846.96891298</v>
       </c>
     </row>
     <row r="56">
@@ -5856,13 +5856,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R56" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S56" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T56" t="n">
         <v>0.00000000</v>
@@ -5877,13 +5877,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X56" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y56" t="n">
-        <v>19984581.60000000</v>
+        <v>19182669.53200000</v>
       </c>
       <c r="Z56" t="n">
-        <v>377726.63839108</v>
+        <v>325328.66441688</v>
       </c>
     </row>
     <row r="57">
@@ -5936,13 +5936,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R57" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S57" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T57" t="n">
         <v>0.00000000</v>
@@ -5957,13 +5957,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X57" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y57" t="n">
-        <v>20841244.45714286</v>
+        <v>19877344.30914286</v>
       </c>
       <c r="Z57" t="n">
-        <v>372144.47132126</v>
+        <v>320872.25248747</v>
       </c>
     </row>
     <row r="58">
@@ -6016,13 +6016,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R58" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S58" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T58" t="n">
         <v>0.00000000</v>
@@ -6037,13 +6037,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X58" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y58" t="n">
-        <v>21697907.31428571</v>
+        <v>20572019.08628571</v>
       </c>
       <c r="Z58" t="n">
-        <v>366644.79933129</v>
+        <v>316476.88530898</v>
       </c>
     </row>
     <row r="59">
@@ -6096,13 +6096,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R59" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S59" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T59" t="n">
         <v>0.00000000</v>
@@ -6117,13 +6117,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X59" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y59" t="n">
-        <v>22554570.17142857</v>
+        <v>21266693.86342857</v>
       </c>
       <c r="Z59" t="n">
-        <v>361226.40328206</v>
+        <v>312141.72667916</v>
       </c>
     </row>
     <row r="60">
@@ -6176,13 +6176,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R60" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S60" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T60" t="n">
         <v>0.00000000</v>
@@ -6197,13 +6197,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X60" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y60" t="n">
-        <v>23411233.02857143</v>
+        <v>21961368.64057143</v>
       </c>
       <c r="Z60" t="n">
-        <v>355888.08205129</v>
+        <v>307865.95185024</v>
       </c>
     </row>
     <row r="61">
@@ -6256,13 +6256,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R61" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S61" t="n">
-        <v>0.00000000</v>
+        <v>156271.20000000</v>
       </c>
       <c r="T61" t="n">
         <v>0.00000000</v>
@@ -6277,13 +6277,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X61" t="n">
-        <v>856662.85714286</v>
+        <v>694674.77714286</v>
       </c>
       <c r="Y61" t="n">
-        <v>24267895.88571429</v>
+        <v>22656043.41771429</v>
       </c>
       <c r="Z61" t="n">
-        <v>350628.65226728</v>
+        <v>303648.74737198</v>
       </c>
     </row>
     <row r="62">
@@ -6336,13 +6336,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R62" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S62" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T62" t="n">
         <v>0.00000000</v>
@@ -6357,13 +6357,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X62" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y62" t="n">
-        <v>25124558.74285714</v>
+        <v>23389785.99485714</v>
       </c>
       <c r="Z62" t="n">
-        <v>345446.94804658</v>
+        <v>316332.28391769</v>
       </c>
     </row>
     <row r="63">
@@ -6416,13 +6416,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R63" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S63" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T63" t="n">
         <v>0.00000000</v>
@@ -6437,13 +6437,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X63" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y63" t="n">
-        <v>25981221.60000000</v>
+        <v>24123528.57200000</v>
       </c>
       <c r="Z63" t="n">
-        <v>340341.82073555</v>
+        <v>311999.10606435</v>
       </c>
     </row>
     <row r="64">
@@ -6496,13 +6496,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R64" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S64" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T64" t="n">
         <v>0.00000000</v>
@@ -6517,13 +6517,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X64" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y64" t="n">
-        <v>26837884.45714286</v>
+        <v>24857271.14914286</v>
       </c>
       <c r="Z64" t="n">
-        <v>335312.13865571</v>
+        <v>307725.28487886</v>
       </c>
     </row>
     <row r="65">
@@ -6576,13 +6576,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R65" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S65" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T65" t="n">
         <v>0.00000000</v>
@@ -6597,13 +6597,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X65" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y65" t="n">
-        <v>27694547.31428571</v>
+        <v>25591013.72628571</v>
       </c>
       <c r="Z65" t="n">
-        <v>330356.78685292</v>
+        <v>303510.00728267</v>
       </c>
     </row>
     <row r="66">
@@ -6656,13 +6656,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R66" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S66" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T66" t="n">
         <v>0.00000000</v>
@@ -6677,13 +6677,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X66" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y66" t="n">
-        <v>28551210.17142857</v>
+        <v>26324756.30342857</v>
       </c>
       <c r="Z66" t="n">
-        <v>325474.66685016</v>
+        <v>299352.47133491</v>
       </c>
     </row>
     <row r="67">
@@ -6736,13 +6736,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R67" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S67" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T67" t="n">
         <v>0.00000000</v>
@@ -6757,13 +6757,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X67" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y67" t="n">
-        <v>29407873.02857143</v>
+        <v>27058498.88057143</v>
       </c>
       <c r="Z67" t="n">
-        <v>320664.69640410</v>
+        <v>295251.88607985</v>
       </c>
     </row>
     <row r="68">
@@ -6816,13 +6816,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R68" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S68" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T68" t="n">
         <v>0.00000000</v>
@@ -6837,13 +6837,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X68" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y68" t="n">
-        <v>30264535.88571429</v>
+        <v>27792241.45771429</v>
       </c>
       <c r="Z68" t="n">
-        <v>315925.80926513</v>
+        <v>291207.47139643</v>
       </c>
     </row>
     <row r="69">
@@ -6896,13 +6896,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R69" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S69" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T69" t="n">
         <v>0.00000000</v>
@@ -6917,13 +6917,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X69" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y69" t="n">
-        <v>31121198.74285714</v>
+        <v>28525984.03485714</v>
       </c>
       <c r="Z69" t="n">
-        <v>311256.95494101</v>
+        <v>287218.45784980</v>
       </c>
     </row>
     <row r="70">
@@ -6976,13 +6976,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R70" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S70" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T70" t="n">
         <v>0.00000000</v>
@@ -6997,13 +6997,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X70" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y70" t="n">
-        <v>31977861.60000000</v>
+        <v>29259726.61200000</v>
       </c>
       <c r="Z70" t="n">
-        <v>306657.09846405</v>
+        <v>283284.08654501</v>
       </c>
     </row>
     <row r="71">
@@ -7056,13 +7056,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R71" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S71" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T71" t="n">
         <v>0.00000000</v>
@@ -7077,13 +7077,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X71" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y71" t="n">
-        <v>32834524.45714286</v>
+        <v>29993469.18914286</v>
       </c>
       <c r="Z71" t="n">
-        <v>302125.22016163</v>
+        <v>279403.60898256</v>
       </c>
     </row>
     <row r="72">
@@ -7136,13 +7136,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R72" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S72" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T72" t="n">
         <v>0.00000000</v>
@@ -7157,13 +7157,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X72" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y72" t="n">
-        <v>33691187.31428571</v>
+        <v>30727211.76628571</v>
       </c>
       <c r="Z72" t="n">
-        <v>297660.31543017</v>
+        <v>275576.28691605</v>
       </c>
     </row>
     <row r="73">
@@ -7216,13 +7216,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R73" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S73" t="n">
-        <v>0.00000000</v>
+        <v>117203.40000000</v>
       </c>
       <c r="T73" t="n">
         <v>0.00000000</v>
@@ -7237,13 +7237,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X73" t="n">
-        <v>856662.85714286</v>
+        <v>733742.57714286</v>
       </c>
       <c r="Y73" t="n">
-        <v>34547850.17142857</v>
+        <v>31460954.34342857</v>
       </c>
       <c r="Z73" t="n">
-        <v>293261.39451249</v>
+        <v>271801.39221172</v>
       </c>
     </row>
     <row r="74">
@@ -7296,13 +7296,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R74" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S74" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T74" t="n">
         <v>0.00000000</v>
@@ -7317,13 +7317,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X74" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y74" t="n">
-        <v>35404513.02857143</v>
+        <v>32214230.82057143</v>
       </c>
       <c r="Z74" t="n">
-        <v>288927.48227831</v>
+        <v>275215.05966785</v>
       </c>
     </row>
     <row r="75">
@@ -7376,13 +7376,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R75" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S75" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T75" t="n">
         <v>0.00000000</v>
@@ -7397,13 +7397,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X75" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y75" t="n">
-        <v>36261175.88571429</v>
+        <v>32967507.29771429</v>
       </c>
       <c r="Z75" t="n">
-        <v>284657.61800819</v>
+        <v>271445.11312085</v>
       </c>
     </row>
     <row r="76">
@@ -7456,13 +7456,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R76" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S76" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T76" t="n">
         <v>0.00000000</v>
@@ -7477,13 +7477,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X76" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y76" t="n">
-        <v>37117838.74285714</v>
+        <v>33720783.77485714</v>
       </c>
       <c r="Z76" t="n">
-        <v>280450.85518048</v>
+        <v>267726.80799560</v>
       </c>
     </row>
     <row r="77">
@@ -7536,13 +7536,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R77" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S77" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T77" t="n">
         <v>0.00000000</v>
@@ -7557,13 +7557,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X77" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y77" t="n">
-        <v>37974501.60000000</v>
+        <v>34474060.25200000</v>
       </c>
       <c r="Z77" t="n">
-        <v>276306.26126156</v>
+        <v>264059.43689840</v>
       </c>
     </row>
     <row r="78">
@@ -7616,13 +7616,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R78" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S78" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T78" t="n">
         <v>0.00000000</v>
@@ -7637,13 +7637,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X78" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y78" t="n">
-        <v>38831164.45714286</v>
+        <v>35227336.72914286</v>
       </c>
       <c r="Z78" t="n">
-        <v>272222.91749907</v>
+        <v>260442.30212555</v>
       </c>
     </row>
     <row r="79">
@@ -7696,13 +7696,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R79" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S79" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T79" t="n">
         <v>0.00000000</v>
@@ -7717,13 +7717,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X79" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y79" t="n">
-        <v>39687827.31428571</v>
+        <v>35980613.20628571</v>
       </c>
       <c r="Z79" t="n">
-        <v>268199.91871830</v>
+        <v>256874.71553063</v>
       </c>
     </row>
     <row r="80">
@@ -7776,13 +7776,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R80" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S80" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T80" t="n">
         <v>0.00000000</v>
@@ -7797,13 +7797,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X80" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y80" t="n">
-        <v>40544490.17142857</v>
+        <v>36733889.68342857</v>
       </c>
       <c r="Z80" t="n">
-        <v>264236.37312148</v>
+        <v>253355.99839359</v>
       </c>
     </row>
     <row r="81">
@@ -7856,13 +7856,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R81" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S81" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T81" t="n">
         <v>0.00000000</v>
@@ -7877,13 +7877,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X81" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y81" t="n">
-        <v>41401153.02857143</v>
+        <v>37487166.16057143</v>
       </c>
       <c r="Z81" t="n">
-        <v>260331.40209012</v>
+        <v>249885.48129160</v>
       </c>
     </row>
     <row r="82">
@@ -7936,13 +7936,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R82" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S82" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T82" t="n">
         <v>0.00000000</v>
@@ -7957,13 +7957,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X82" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y82" t="n">
-        <v>42257815.88571429</v>
+        <v>38240442.63771429</v>
       </c>
       <c r="Z82" t="n">
-        <v>256484.13999027</v>
+        <v>246462.50397169</v>
       </c>
     </row>
     <row r="83">
@@ -8016,13 +8016,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R83" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S83" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T83" t="n">
         <v>0.00000000</v>
@@ -8037,13 +8037,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X83" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y83" t="n">
-        <v>43114478.74285714</v>
+        <v>38993719.11485714</v>
       </c>
       <c r="Z83" t="n">
-        <v>252693.73398056</v>
+        <v>243086.41522519</v>
       </c>
     </row>
     <row r="84">
@@ -8096,13 +8096,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R84" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S84" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T84" t="n">
         <v>0.00000000</v>
@@ -8117,13 +8117,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X84" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y84" t="n">
-        <v>43971141.60000000</v>
+        <v>39746995.59200000</v>
       </c>
       <c r="Z84" t="n">
-        <v>248959.34382321</v>
+        <v>239756.57276379</v>
       </c>
     </row>
     <row r="85">
@@ -8176,13 +8176,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R85" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S85" t="n">
-        <v>0.00000000</v>
+        <v>97669.50000000</v>
       </c>
       <c r="T85" t="n">
         <v>0.00000000</v>
@@ -8197,13 +8197,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X85" t="n">
-        <v>856662.85714286</v>
+        <v>753276.47714286</v>
       </c>
       <c r="Y85" t="n">
-        <v>44827804.45714286</v>
+        <v>40500272.06914286</v>
       </c>
       <c r="Z85" t="n">
-        <v>245280.14169775</v>
+        <v>236472.34309735</v>
       </c>
     </row>
     <row r="86">
@@ -8256,13 +8256,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R86" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S86" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T86" t="n">
         <v>0.00000000</v>
@@ -8277,13 +8277,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X86" t="n">
-        <v>856662.85714286</v>
+        <v>772810.37714286</v>
       </c>
       <c r="Y86" t="n">
-        <v>45684467.31428571</v>
+        <v>41273082.44628571</v>
       </c>
       <c r="Z86" t="n">
-        <v>241655.31201748</v>
+        <v>239281.28188626</v>
       </c>
     </row>
     <row r="87">
@@ -8336,13 +8336,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R87" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S87" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T87" t="n">
         <v>0.00000000</v>
@@ -8357,13 +8357,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X87" t="n">
-        <v>856662.85714286</v>
+        <v>772810.37714286</v>
       </c>
       <c r="Y87" t="n">
-        <v>46541130.17142857</v>
+        <v>42045892.82342857</v>
       </c>
       <c r="Z87" t="n">
-        <v>238084.05124875</v>
+        <v>236003.56284176</v>
       </c>
     </row>
     <row r="88">
@@ -8416,13 +8416,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R88" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S88" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T88" t="n">
         <v>0.00000000</v>
@@ -8437,13 +8437,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X88" t="n">
-        <v>856662.85714286</v>
+        <v>772810.37714286</v>
       </c>
       <c r="Y88" t="n">
-        <v>47397793.02857143</v>
+        <v>42818703.20057143</v>
       </c>
       <c r="Z88" t="n">
-        <v>234565.56773276</v>
+        <v>232770.74259606</v>
       </c>
     </row>
     <row r="89">
@@ -8496,13 +8496,13 @@
         <v>921142.85714286</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00000000</v>
+        <v>5716.88000000</v>
       </c>
       <c r="R89" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S89" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T89" t="n">
         <v>0.00000000</v>
@@ -8517,13 +8517,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X89" t="n">
-        <v>856662.85714286</v>
+        <v>772810.37714286</v>
       </c>
       <c r="Y89" t="n">
-        <v>48254455.88571429</v>
+        <v>43591513.57771429</v>
       </c>
       <c r="Z89" t="n">
-        <v>231099.08151011</v>
+        <v>229582.20611717</v>
       </c>
     </row>
     <row r="90">
@@ -8576,13 +8576,13 @@
         <v>896342.85714286</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.00000000</v>
+        <v>5562.96400000</v>
       </c>
       <c r="R90" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S90" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T90" t="n">
         <v>0.00000000</v>
@@ -8597,13 +8597,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X90" t="n">
-        <v>833598.85714286</v>
+        <v>749900.29314286</v>
       </c>
       <c r="Y90" t="n">
-        <v>49088054.74285714</v>
+        <v>44341413.87085714</v>
       </c>
       <c r="Z90" t="n">
-        <v>221553.87503622</v>
+        <v>219724.57638317</v>
       </c>
     </row>
     <row r="91">
@@ -8656,13 +8656,13 @@
         <v>871542.85714286</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.00000000</v>
+        <v>5409.04800000</v>
       </c>
       <c r="R91" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S91" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T91" t="n">
         <v>0.00000000</v>
@@ -8677,13 +8677,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X91" t="n">
-        <v>810534.85714286</v>
+        <v>726990.20914286</v>
       </c>
       <c r="Y91" t="n">
-        <v>49898589.60000000</v>
+        <v>45068404.08000000</v>
       </c>
       <c r="Z91" t="n">
-        <v>212240.32110792</v>
+        <v>210093.93104056</v>
       </c>
     </row>
     <row r="92">
@@ -8736,13 +8736,13 @@
         <v>846742.85714286</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.00000000</v>
+        <v>5255.13200000</v>
       </c>
       <c r="R92" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S92" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T92" t="n">
         <v>0.00000000</v>
@@ -8757,13 +8757,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X92" t="n">
-        <v>787470.85714286</v>
+        <v>704080.12514286</v>
       </c>
       <c r="Y92" t="n">
-        <v>50686060.45714286</v>
+        <v>45772484.20514286</v>
       </c>
       <c r="Z92" t="n">
-        <v>203153.65751449</v>
+        <v>200685.90122948</v>
       </c>
     </row>
     <row r="93">
@@ -8816,13 +8816,13 @@
         <v>821942.85714286</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.00000000</v>
+        <v>5101.21600000</v>
       </c>
       <c r="R93" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S93" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T93" t="n">
         <v>0.00000000</v>
@@ -8837,13 +8837,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X93" t="n">
-        <v>764406.85714286</v>
+        <v>681170.04114286</v>
       </c>
       <c r="Y93" t="n">
-        <v>51450467.31428571</v>
+        <v>46453654.24628571</v>
       </c>
       <c r="Z93" t="n">
-        <v>194289.21220753</v>
+        <v>191496.19518955</v>
       </c>
     </row>
     <row r="94">
@@ -8896,13 +8896,13 @@
         <v>797142.85714286</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.00000000</v>
+        <v>4947.30000000</v>
       </c>
       <c r="R94" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S94" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T94" t="n">
         <v>0.00000000</v>
@@ -8917,13 +8917,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X94" t="n">
-        <v>741342.85714286</v>
+        <v>658259.95714286</v>
       </c>
       <c r="Y94" t="n">
-        <v>52191810.17142857</v>
+        <v>47111914.20342857</v>
       </c>
       <c r="Z94" t="n">
-        <v>185642.40167612</v>
+        <v>182520.59696738</v>
       </c>
     </row>
     <row r="95">
@@ -8976,13 +8976,13 @@
         <v>772342.85714286</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.00000000</v>
+        <v>4793.38400000</v>
       </c>
       <c r="R95" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S95" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T95" t="n">
         <v>0.00000000</v>
@@ -8997,13 +8997,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X95" t="n">
-        <v>718278.85714286</v>
+        <v>635349.87314286</v>
       </c>
       <c r="Y95" t="n">
-        <v>52910089.02857143</v>
+        <v>47747264.07657143</v>
       </c>
       <c r="Z95" t="n">
-        <v>177208.72935039</v>
+        <v>173754.96514509</v>
       </c>
     </row>
     <row r="96">
@@ -9056,13 +9056,13 @@
         <v>747542.85714286</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.00000000</v>
+        <v>4639.46800000</v>
       </c>
       <c r="R96" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S96" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T96" t="n">
         <v>0.00000000</v>
@@ -9077,13 +9077,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X96" t="n">
-        <v>695214.85714286</v>
+        <v>612439.78914286</v>
       </c>
       <c r="Y96" t="n">
-        <v>53605303.88571429</v>
+        <v>48359703.86571429</v>
       </c>
       <c r="Z96" t="n">
-        <v>168983.78403277</v>
+        <v>165195.23158936</v>
       </c>
     </row>
     <row r="97">
@@ -9136,13 +9136,13 @@
         <v>722742.85714286</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.00000000</v>
+        <v>4485.55200000</v>
       </c>
       <c r="R97" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S97" t="n">
-        <v>0.00000000</v>
+        <v>78135.60000000</v>
       </c>
       <c r="T97" t="n">
         <v>0.00000000</v>
@@ -9157,13 +9157,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X97" t="n">
-        <v>672150.85714286</v>
+        <v>589529.70514286</v>
       </c>
       <c r="Y97" t="n">
-        <v>54277454.74285714</v>
+        <v>48949233.57085714</v>
       </c>
       <c r="Z97" t="n">
-        <v>160963.23835681</v>
+        <v>156837.40022079</v>
       </c>
     </row>
     <row r="98">
@@ -9216,13 +9216,13 @@
         <v>697942.85714286</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.00000000</v>
+        <v>4331.63600000</v>
       </c>
       <c r="R98" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S98" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T98" t="n">
         <v>0.00000000</v>
@@ -9237,13 +9237,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X98" t="n">
-        <v>649086.85714286</v>
+        <v>586153.52114286</v>
       </c>
       <c r="Y98" t="n">
-        <v>54926541.60000000</v>
+        <v>49535387.09200000</v>
       </c>
       <c r="Z98" t="n">
-        <v>153142.84727273</v>
+        <v>153803.12247515</v>
       </c>
     </row>
     <row r="99">
@@ -9296,13 +9296,13 @@
         <v>673142.85714286</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.00000000</v>
+        <v>4177.72000000</v>
       </c>
       <c r="R99" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S99" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T99" t="n">
         <v>0.00000000</v>
@@ -9317,13 +9317,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X99" t="n">
-        <v>626022.85714286</v>
+        <v>563243.43714286</v>
       </c>
       <c r="Y99" t="n">
-        <v>55552564.45714286</v>
+        <v>50098630.52914286</v>
       </c>
       <c r="Z99" t="n">
-        <v>145518.44655957</v>
+        <v>145767.17833203</v>
       </c>
     </row>
     <row r="100">
@@ -9376,13 +9376,13 @@
         <v>648342.85714286</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.00000000</v>
+        <v>4023.80400000</v>
       </c>
       <c r="R100" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S100" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T100" t="n">
         <v>0.00000000</v>
@@ -9397,13 +9397,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X100" t="n">
-        <v>602958.85714286</v>
+        <v>540333.35314286</v>
       </c>
       <c r="Y100" t="n">
-        <v>56155523.31428571</v>
+        <v>50638963.88228571</v>
       </c>
       <c r="Z100" t="n">
-        <v>138085.95136324</v>
+        <v>137922.53021717</v>
       </c>
     </row>
     <row r="101">
@@ -9456,13 +9456,13 @@
         <v>623542.85714286</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.00000000</v>
+        <v>3869.88800000</v>
       </c>
       <c r="R101" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S101" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T101" t="n">
         <v>0.00000000</v>
@@ -9477,13 +9477,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X101" t="n">
-        <v>579894.85714286</v>
+        <v>517423.26914286</v>
       </c>
       <c r="Y101" t="n">
-        <v>56735418.17142857</v>
+        <v>51156387.15142857</v>
       </c>
       <c r="Z101" t="n">
-        <v>130841.35476018</v>
+        <v>130265.44518072</v>
       </c>
     </row>
     <row r="102">
@@ -9536,13 +9536,13 @@
         <v>598742.85714286</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.00000000</v>
+        <v>3715.97200000</v>
       </c>
       <c r="R102" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S102" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T102" t="n">
         <v>0.00000000</v>
@@ -9557,13 +9557,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X102" t="n">
-        <v>556830.85714286</v>
+        <v>494513.18514286</v>
       </c>
       <c r="Y102" t="n">
-        <v>57292249.02857143</v>
+        <v>51650900.33657143</v>
       </c>
       <c r="Z102" t="n">
-        <v>123780.72634612</v>
+        <v>122792.25664723</v>
       </c>
     </row>
     <row r="103">
@@ -9616,13 +9616,13 @@
         <v>573942.85714286</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.00000000</v>
+        <v>3562.05600000</v>
       </c>
       <c r="R103" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S103" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T103" t="n">
         <v>0.00000000</v>
@@ -9637,13 +9637,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X103" t="n">
-        <v>533766.85714286</v>
+        <v>471603.10114286</v>
       </c>
       <c r="Y103" t="n">
-        <v>57826015.88571429</v>
+        <v>52122503.43771429</v>
       </c>
       <c r="Z103" t="n">
-        <v>116900.21084952</v>
+        <v>115499.36329772</v>
       </c>
     </row>
     <row r="104">
@@ -9696,13 +9696,13 @@
         <v>549142.85714286</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.00000000</v>
+        <v>3408.14000000</v>
       </c>
       <c r="R104" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S104" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T104" t="n">
         <v>0.00000000</v>
@@ -9717,13 +9717,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X104" t="n">
-        <v>510702.85714286</v>
+        <v>448693.01714286</v>
       </c>
       <c r="Y104" t="n">
-        <v>58336718.74285714</v>
+        <v>52571196.45485714</v>
       </c>
       <c r="Z104" t="n">
-        <v>110196.02676929</v>
+        <v>108383.22796992</v>
       </c>
     </row>
     <row r="105">
@@ -9776,13 +9776,13 @@
         <v>524342.85714286</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.00000000</v>
+        <v>3254.22400000</v>
       </c>
       <c r="R105" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S105" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T105" t="n">
         <v>0.00000000</v>
@@ -9797,13 +9797,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X105" t="n">
-        <v>487638.85714286</v>
+        <v>425782.93314286</v>
       </c>
       <c r="Y105" t="n">
-        <v>58824357.60000000</v>
+        <v>52996979.38800000</v>
       </c>
       <c r="Z105" t="n">
-        <v>103664.46503642</v>
+        <v>101440.37657629</v>
       </c>
     </row>
     <row r="106">
@@ -9856,13 +9856,13 @@
         <v>499542.85714286</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.00000000</v>
+        <v>3100.30800000</v>
       </c>
       <c r="R106" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S106" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T106" t="n">
         <v>0.00000000</v>
@@ -9877,13 +9877,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X106" t="n">
-        <v>464574.85714286</v>
+        <v>402872.84914286</v>
       </c>
       <c r="Y106" t="n">
-        <v>59288932.45714286</v>
+        <v>53399852.23714286</v>
       </c>
       <c r="Z106" t="n">
-        <v>97301.88769895</v>
+        <v>94667.39703977</v>
       </c>
     </row>
     <row r="107">
@@ -9936,13 +9936,13 @@
         <v>474742.85714286</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.00000000</v>
+        <v>2946.39200000</v>
       </c>
       <c r="R107" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S107" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T107" t="n">
         <v>0.00000000</v>
@@ -9957,13 +9957,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X107" t="n">
-        <v>441510.85714286</v>
+        <v>379962.76514286</v>
       </c>
       <c r="Y107" t="n">
-        <v>59730443.31428571</v>
+        <v>53779815.00228571</v>
       </c>
       <c r="Z107" t="n">
-        <v>91104.72663004</v>
+        <v>88060.93824676</v>
       </c>
     </row>
     <row r="108">
@@ -10016,13 +10016,13 @@
         <v>449942.85714286</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.00000000</v>
+        <v>2792.47600000</v>
       </c>
       <c r="R108" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S108" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T108" t="n">
         <v>0.00000000</v>
@@ -10037,13 +10037,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X108" t="n">
-        <v>418446.85714286</v>
+        <v>357052.68114286</v>
       </c>
       <c r="Y108" t="n">
-        <v>60148890.17142857</v>
+        <v>54136867.68342857</v>
       </c>
       <c r="Z108" t="n">
-        <v>85069.48225877</v>
+        <v>81617.70901724</v>
       </c>
     </row>
     <row r="109">
@@ -10096,13 +10096,13 @@
         <v>425142.85714286</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.00000000</v>
+        <v>2638.56000000</v>
       </c>
       <c r="R109" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S109" t="n">
-        <v>0.00000000</v>
+        <v>58601.70000000</v>
       </c>
       <c r="T109" t="n">
         <v>0.00000000</v>
@@ -10117,13 +10117,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X109" t="n">
-        <v>395382.85714286</v>
+        <v>334142.59714286</v>
       </c>
       <c r="Y109" t="n">
-        <v>60544273.02857143</v>
+        <v>54471010.28057143</v>
       </c>
       <c r="Z109" t="n">
-        <v>79192.72232305</v>
+        <v>75334.47709155</v>
       </c>
     </row>
     <row r="110">
@@ -10176,13 +10176,13 @@
         <v>400342.85714286</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.00000000</v>
+        <v>2484.64400000</v>
       </c>
       <c r="R110" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S110" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T110" t="n">
         <v>0.00000000</v>
@@ -10197,13 +10197,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X110" t="n">
-        <v>372318.85714286</v>
+        <v>330766.41314286</v>
       </c>
       <c r="Y110" t="n">
-        <v>60916591.88571429</v>
+        <v>54801776.69371429</v>
       </c>
       <c r="Z110" t="n">
-        <v>73471.08064454</v>
+        <v>73551.77717774</v>
       </c>
     </row>
     <row r="111">
@@ -10256,13 +10256,13 @@
         <v>375542.85714286</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.00000000</v>
+        <v>2330.72800000</v>
       </c>
       <c r="R111" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S111" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T111" t="n">
         <v>0.00000000</v>
@@ -10277,13 +10277,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X111" t="n">
-        <v>349254.85714286</v>
+        <v>307856.32914286</v>
       </c>
       <c r="Y111" t="n">
-        <v>61265846.74285714</v>
+        <v>55109633.02285714</v>
       </c>
       <c r="Z111" t="n">
-        <v>67901.25592503</v>
+        <v>67519.57286925</v>
       </c>
     </row>
     <row r="112">
@@ -10336,13 +10336,13 @@
         <v>350742.85714286</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.00000000</v>
+        <v>2176.81200000</v>
       </c>
       <c r="R112" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S112" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T112" t="n">
         <v>0.00000000</v>
@@ -10357,13 +10357,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X112" t="n">
-        <v>326190.85714286</v>
+        <v>284946.24514286</v>
       </c>
       <c r="Y112" t="n">
-        <v>61592037.60000000</v>
+        <v>55394579.26800000</v>
       </c>
       <c r="Z112" t="n">
-        <v>62480.01056397</v>
+        <v>61638.82777710</v>
       </c>
     </row>
     <row r="113">
@@ -10416,13 +10416,13 @@
         <v>325942.85714286</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.00000000</v>
+        <v>2022.89600000</v>
       </c>
       <c r="R113" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S113" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T113" t="n">
         <v>0.00000000</v>
@@ -10437,13 +10437,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X113" t="n">
-        <v>303126.85714286</v>
+        <v>262036.16114286</v>
       </c>
       <c r="Y113" t="n">
-        <v>61895164.45714286</v>
+        <v>55656615.42914286</v>
       </c>
       <c r="Z113" t="n">
-        <v>57204.16949679</v>
+        <v>55906.52435315</v>
       </c>
     </row>
     <row r="114">
@@ -10496,13 +10496,13 @@
         <v>301142.85714286</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.00000000</v>
+        <v>1868.98000000</v>
       </c>
       <c r="R114" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S114" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T114" t="n">
         <v>0.00000000</v>
@@ -10517,13 +10517,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X114" t="n">
-        <v>280062.85714286</v>
+        <v>239126.07714286</v>
       </c>
       <c r="Y114" t="n">
-        <v>62175227.31428571</v>
+        <v>55895741.50628571</v>
       </c>
       <c r="Z114" t="n">
-        <v>52070.61905362</v>
+        <v>50319.69929926</v>
       </c>
     </row>
     <row r="115">
@@ -10576,13 +10576,13 @@
         <v>276342.85714286</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.00000000</v>
+        <v>1715.06400000</v>
       </c>
       <c r="R115" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S115" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T115" t="n">
         <v>0.00000000</v>
@@ -10597,13 +10597,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X115" t="n">
-        <v>256998.85714286</v>
+        <v>216215.99314286</v>
       </c>
       <c r="Y115" t="n">
-        <v>62432226.17142857</v>
+        <v>56111957.49942857</v>
       </c>
       <c r="Z115" t="n">
-        <v>47076.30583811</v>
+        <v>44875.44264728</v>
       </c>
     </row>
     <row r="116">
@@ -10656,13 +10656,13 @@
         <v>251542.85714286</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.00000000</v>
+        <v>1561.14800000</v>
       </c>
       <c r="R116" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S116" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T116" t="n">
         <v>0.00000000</v>
@@ -10677,13 +10677,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X116" t="n">
-        <v>233934.85714286</v>
+        <v>193305.90914286</v>
       </c>
       <c r="Y116" t="n">
-        <v>62666161.02857143</v>
+        <v>56305263.40857143</v>
       </c>
       <c r="Z116" t="n">
-        <v>42218.23562594</v>
+        <v>39570.89685402</v>
       </c>
     </row>
     <row r="117">
@@ -10736,13 +10736,13 @@
         <v>226742.85714286</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.00000000</v>
+        <v>1407.23200000</v>
       </c>
       <c r="R117" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S117" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T117" t="n">
         <v>0.00000000</v>
@@ -10757,13 +10757,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X117" t="n">
-        <v>210870.85714286</v>
+        <v>170395.82514286</v>
       </c>
       <c r="Y117" t="n">
-        <v>62877031.88571429</v>
+        <v>56475659.23371429</v>
       </c>
       <c r="Z117" t="n">
-        <v>37493.47228280</v>
+        <v>34403.25591102</v>
       </c>
     </row>
     <row r="118">
@@ -10816,13 +10816,13 @@
         <v>201942.85714286</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.00000000</v>
+        <v>1253.31600000</v>
       </c>
       <c r="R118" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S118" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T118" t="n">
         <v>0.00000000</v>
@@ -10837,13 +10837,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X118" t="n">
-        <v>187806.85714286</v>
+        <v>147485.74114286</v>
       </c>
       <c r="Y118" t="n">
-        <v>63064838.74285714</v>
+        <v>56623144.97485714</v>
       </c>
       <c r="Z118" t="n">
-        <v>32899.13670135</v>
+        <v>29369.76446888</v>
       </c>
     </row>
     <row r="119">
@@ -10896,13 +10896,13 @@
         <v>177142.85714286</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.00000000</v>
+        <v>1099.40000000</v>
       </c>
       <c r="R119" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S119" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T119" t="n">
         <v>0.00000000</v>
@@ -10917,13 +10917,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X119" t="n">
-        <v>164742.85714286</v>
+        <v>124575.65714286</v>
       </c>
       <c r="Y119" t="n">
-        <v>63229581.60000000</v>
+        <v>56747720.63200000</v>
       </c>
       <c r="Z119" t="n">
-        <v>28432.40575694</v>
+        <v>24467.71697592</v>
       </c>
     </row>
     <row r="120">
@@ -10976,13 +10976,13 @@
         <v>152342.85714286</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.00000000</v>
+        <v>945.48400000</v>
       </c>
       <c r="R120" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S120" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T120" t="n">
         <v>0.00000000</v>
@@ -10997,13 +10997,13 @@
         <v>0.00000000</v>
       </c>
       <c r="X120" t="n">
-        <v>141678.85714286</v>
+        <v>101665.57314286</v>
       </c>
       <c r="Y120" t="n">
-        <v>63371260.45714286</v>
+        <v>56849386.20514286</v>
       </c>
       <c r="Z120" t="n">
-        <v>24090.51128174</v>
+        <v>19694.45683089</v>
       </c>
     </row>
     <row r="121">
@@ -11056,13 +11056,13 @@
         <v>127542.85714286</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.00000000</v>
+        <v>791.56800000</v>
       </c>
       <c r="R121" t="n">
         <v>0.00000000</v>
       </c>
       <c r="S121" t="n">
-        <v>0.00000000</v>
+        <v>39067.80000000</v>
       </c>
       <c r="T121" t="n">
         <v>0.00000000</v>
@@ -11077,13 +11077,1933 @@
         <v>0.00000000</v>
       </c>
       <c r="X121" t="n">
-        <v>118614.85714286</v>
+        <v>78755.48914286</v>
       </c>
       <c r="Y121" t="n">
-        <v>63489875.31428571</v>
+        <v>56928141.69428571</v>
       </c>
       <c r="Z121" t="n">
-        <v>19870.73905700</v>
+        <v>15047.37554960</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H122" t="n">
+        <v>102742.85714286</v>
+      </c>
+      <c r="I122" t="n">
+        <v>102742.85714286</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K122" t="n">
+        <v>25685.71428571</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P122" t="n">
+        <v>102742.85714286</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>637.65200000</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S122" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X122" t="n">
+        <v>75379.30514286</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>57003520.99942857</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>14205.02130445</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H123" t="n">
+        <v>77942.85714286</v>
+      </c>
+      <c r="I123" t="n">
+        <v>77942.85714286</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K123" t="n">
+        <v>19485.71428571</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P123" t="n">
+        <v>77942.85714286</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>483.73600000</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S123" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X123" t="n">
+        <v>52469.22114286</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>57055990.22057143</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>9752.23616735</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H124" t="n">
+        <v>53142.85714286</v>
+      </c>
+      <c r="I124" t="n">
+        <v>53142.85714286</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K124" t="n">
+        <v>13285.71428571</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P124" t="n">
+        <v>53142.85714286</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>329.82000000</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S124" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X124" t="n">
+        <v>29559.13714286</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>57085549.35771429</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>5418.77573743</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H125" t="n">
+        <v>28342.85714286</v>
+      </c>
+      <c r="I125" t="n">
+        <v>28342.85714286</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K125" t="n">
+        <v>7085.71428571</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P125" t="n">
+        <v>28342.85714286</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>175.90400000</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S125" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X125" t="n">
+        <v>6649.05314286</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>57092198.41085714</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1202.20647279</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3542.85714286</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3542.85714286</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K126" t="n">
+        <v>885.71428571</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3542.85714286</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>21.98800000</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S126" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-16261.03085714</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>57075937.38000000</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-2899.86088838</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S127" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>57056403.48000000</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-3435.80006359</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S128" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X128" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>57036869.58000000</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>-3388.73584188</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S129" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X129" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>57017335.68000000</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-3342.31631454</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S130" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X130" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>56997801.78000000</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-3296.53265044</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S131" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X131" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>56978267.88000000</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-3251.37613939</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S132" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X132" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>56958733.98000000</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-3206.83819054</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S133" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>56939200.08000000</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-3162.91033071</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S134" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>56919666.18000000</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-3119.58420280</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S135" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>56900132.28000000</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-3076.85156416</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S136" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>56880598.38000000</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-3034.70428507</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S137" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>56861064.48000000</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-2993.13434716</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S138" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>56841530.58000000</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-2952.13384192</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S139" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X139" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>56821996.68000000</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-2911.69496914</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S140" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X140" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>56802462.78000000</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-2871.81003549</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S141" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X141" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>56782928.88000000</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-2832.47145300</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S142" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>56763394.98000000</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>-2793.67173766</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S143" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>56743861.08000000</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-2755.40350796</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S144" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>56724327.18000000</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>-2717.65948351</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>600.00000000</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="S145" t="n">
+        <v>19533.90000000</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0.00000000</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-19533.90000000</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>56704793.28000000</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>-2680.43248366</v>
       </c>
     </row>
   </sheetData>
@@ -11160,7 +13080,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51fb85c0a3e32f0142c12a1ab4b6940fed9a8d654ff6e99ec866554dd9c54da1</t>
+          <t xml:space="preserve">a71543b57e2f339eea210b6559246b5df2bb9efd2f841bcd73dfef495b71edef</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11170,12 +13090,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">476ca585bda3c181ccb13ae7f2b5f694452d006001c77bb20b280e84d7e08cb1</t>
+          <t xml:space="preserve">278f95fc5b9d7dae65f028411ae952a1c60cde933e54714c71c120bff64ae48b</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11202,19 +13122,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">r1ADvAnpxrrUO2jqC26Wd</t>
+          <t xml:space="preserve">81k_JA0ROBKLLwd2z4uSV</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>23648702.90012526</v>
+        <v>23086488.47142834</v>
       </c>
       <c r="G3" t="n">
-        <v>63489875.31428571</v>
+        <v>56704793.28000000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -11227,7 +13147,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -11341,7 +13261,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77110285.71428571</v>
+        <v>77376000.00000000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -11371,7 +13291,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87094285.71428571</v>
+        <v>87360000.00000000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -11401,7 +13321,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31885.71428571</v>
+        <v>0.00000000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -11440,7 +13360,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">paymentFees_month = netContracts_month × 512; variableCosts_month = netContracts_month × (153.92 + 25 + 400); taxes_month = grossReceivablesSettled_month × 0.07</t>
+          <t xml:space="preserve">paymentFees_month = netContracts_month × 512; variableCosts_month = netContracts_month × 425 + Σ(netContracts_cohort × price × 0.5497% / 84) de cohortMonth+4..+87; taxes_month = grossReceivablesSettled_month × 7%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11491,7 +13411,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1875053.96000000</v>
+        <v>1785475.29600000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -11500,7 +13420,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPV mensal pela taxa nominal/12; IRR mensal anualizada; payback interpolado; capital = max(0, -min(caixa acumulado))</t>
+          <t xml:space="preserve">NPV = -preOp(t0) + Σ operatingFlow_month/(1+monthlyEquivalentRate)^month; IRR = annualize(IRR([-preOp, operating M1..M144])); payback = primeiro mês com caixa acumulado &gt;= 0; capital = max(0, -min(caixa acumulado exibido))</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -11521,7 +13441,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23648702.90012526</v>
+        <v>23086488.47142834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -11530,7 +13450,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPV mensal pela taxa nominal/12; IRR mensal anualizada; payback interpolado; capital = max(0, -min(caixa acumulado))</t>
+          <t xml:space="preserve">NPV = -preOp(t0) + Σ operatingFlow_month/(1+monthlyEquivalentRate)^month; IRR = annualize(IRR([-preOp, operating M1..M144])); payback = primeiro mês com caixa acumulado &gt;= 0; capital = max(0, -min(caixa acumulado exibido))</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11551,7 +13471,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.54292981</v>
+        <v>1.55502778</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -11560,7 +13480,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPV mensal pela taxa nominal/12; IRR mensal anualizada; payback interpolado; capital = max(0, -min(caixa acumulado))</t>
+          <t xml:space="preserve">NPV = -preOp(t0) + Σ operatingFlow_month/(1+monthlyEquivalentRate)^month; IRR = annualize(IRR([-preOp, operating M1..M144])); payback = primeiro mês com caixa acumulado &gt;= 0; capital = max(0, -min(caixa acumulado exibido))</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -11581,7 +13501,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.44944585</v>
+        <v>22.00000000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -11590,7 +13510,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPV mensal pela taxa nominal/12; IRR mensal anualizada; payback interpolado; capital = max(0, -min(caixa acumulado))</t>
+          <t xml:space="preserve">NPV = -preOp(t0) + Σ operatingFlow_month/(1+monthlyEquivalentRate)^month; IRR = annualize(IRR([-preOp, operating M1..M144])); payback = primeiro mês com caixa acumulado &gt;= 0; capital = max(0, -min(caixa acumulado exibido))</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -11647,7 +13567,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124824000.00000000</v>
+        <v>124796000.00000000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11656,7 +13576,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11681,7 +13601,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11706,7 +13626,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -11722,7 +13642,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87094285.71428571</v>
+        <v>87360000.00000000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -11731,7 +13651,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11747,7 +13667,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77110285.71428571</v>
+        <v>77376000.00000000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -11756,7 +13676,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -11772,7 +13692,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37464000.00000000</v>
+        <v>37436000.00000000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -11781,7 +13701,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11797,7 +13717,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31885.71428571</v>
+        <v>0.00000000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -11806,7 +13726,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -11831,7 +13751,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -11856,7 +13776,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11881,7 +13801,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -11897,7 +13817,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87094285.71428571</v>
+        <v>87360000.00000000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -11906,7 +13826,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -11931,7 +13851,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -11956,7 +13876,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11972,7 +13892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63489875.31428571</v>
+        <v>56704793.28000000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -11981,7 +13901,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -11997,7 +13917,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23648702.90012526</v>
+        <v>23086488.47142834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -12006,7 +13926,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -12022,7 +13942,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.54292981</v>
+        <v>1.55502778</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -12031,7 +13951,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -12047,7 +13967,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22.44944585</v>
+        <v>22.00000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -12056,7 +13976,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -12083,7 +14003,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12105,7 +14025,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12127,7 +14047,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12149,7 +14069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12161,7 +14081,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12171,7 +14091,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12183,7 +14103,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">r1ADvAnpxrrUO2jqC26Wd</t>
+          <t xml:space="preserve">81k_JA0ROBKLLwd2z4uSV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12193,7 +14113,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12205,7 +14125,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No6RNa-Eqz5ab2ZXuSkse</t>
+          <t xml:space="preserve">x0c6XYXMuJ-Dy1zuDuvsr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12215,7 +14135,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12227,7 +14147,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T20:16:47.517Z</t>
+          <t xml:space="preserve">2026-09-01T21:46:57.629Z</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12237,7 +14157,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12259,7 +14179,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12281,7 +14201,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12303,7 +14223,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
@@ -12315,7 +14235,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">51fb85c0a3e32f0142c12a1ab4b6940fed9a8d654ff6e99ec866554dd9c54da1</t>
+          <t xml:space="preserve">a71543b57e2f339eea210b6559246b5df2bb9efd2f841bcd73dfef495b71edef</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12325,7 +14245,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdff5550a144d036ad5df81fc6427dd3bc96f45636ac057f6f5da496d00a9fa7</t>
+          <t xml:space="preserve">43318f57675ae82fa0d6005a27e08ed2671a4458e3c5677f6d15dac078cbe3bd</t>
         </is>
       </c>
     </row>
